--- a/output_data/charts/0500000US39127.xlsx
+++ b/output_data/charts/0500000US39127.xlsx
@@ -161,10 +161,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>2012</c:v>
                 </c:pt>
@@ -200,51 +200,57 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:f>Sheet1!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>2.476768654909775</c:v>
+                  <c:v>1.210450846384477</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.385399138297676</c:v>
+                  <c:v>1.821409419552876</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2.394848414965141</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.053546879296123</c:v>
+                  <c:v>2.148061589221886</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.184296944969649</c:v>
+                  <c:v>2.084784555677182</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2.190891412082053</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.099075750952351</c:v>
+                  <c:v>2.21694872915756</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.978960524945318</c:v>
+                  <c:v>2.066748999360186</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.632222429987198</c:v>
+                  <c:v>2.630592820205351</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.504210804716101</c:v>
+                  <c:v>2.490290789125684</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.568061549018831</c:v>
+                  <c:v>2.787785211871676</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.996834216307017</c:v>
+                  <c:v>3.015247447990697</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.771950131423473</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -658,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -677,7 +683,7 @@
         <v>2012</v>
       </c>
       <c r="B2" s="1">
-        <v>2.476768654909775</v>
+        <v>1.210450846384477</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -685,7 +691,7 @@
         <v>2013</v>
       </c>
       <c r="B3" s="1">
-        <v>2.385399138297676</v>
+        <v>1.821409419552876</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -701,7 +707,7 @@
         <v>2015</v>
       </c>
       <c r="B5" s="1">
-        <v>2.053546879296123</v>
+        <v>2.148061589221886</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -709,7 +715,7 @@
         <v>2016</v>
       </c>
       <c r="B6" s="1">
-        <v>2.184296944969649</v>
+        <v>2.084784555677182</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -725,7 +731,7 @@
         <v>2018</v>
       </c>
       <c r="B8" s="1">
-        <v>2.099075750952351</v>
+        <v>2.21694872915756</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -733,7 +739,7 @@
         <v>2019</v>
       </c>
       <c r="B9" s="1">
-        <v>1.978960524945318</v>
+        <v>2.066748999360186</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -741,7 +747,7 @@
         <v>2020</v>
       </c>
       <c r="B10" s="1">
-        <v>2.632222429987198</v>
+        <v>2.630592820205351</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -749,7 +755,7 @@
         <v>2021</v>
       </c>
       <c r="B11" s="1">
-        <v>2.504210804716101</v>
+        <v>2.490290789125684</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -757,7 +763,7 @@
         <v>2022</v>
       </c>
       <c r="B12" s="1">
-        <v>2.568061549018831</v>
+        <v>2.787785211871676</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -765,7 +771,15 @@
         <v>2023</v>
       </c>
       <c r="B13" s="1">
-        <v>2.996834216307017</v>
+        <v>3.015247447990697</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2.771950131423473</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39127.xlsx
+++ b/output_data/charts/0500000US39127.xlsx
@@ -161,47 +161,32 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
+              <c:f>Sheet1!$A$2:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2012</c:v>
+                  <c:v>2017</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2013</c:v>
+                  <c:v>2018</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2014</c:v>
+                  <c:v>2019</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2015</c:v>
+                  <c:v>2020</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2016</c:v>
+                  <c:v>2021</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2017</c:v>
+                  <c:v>2022</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2018</c:v>
+                  <c:v>2023</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="12">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -209,47 +194,32 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$14</c:f>
+              <c:f>Sheet1!$B$2:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1.210450846384477</c:v>
+                  <c:v>2.1940279781695</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.821409419552876</c:v>
+                  <c:v>2.248173359145694</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.394848414965141</c:v>
+                  <c:v>2.081628401803384</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.148061589221886</c:v>
+                  <c:v>2.630592820205351</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.084784555677182</c:v>
+                  <c:v>2.490290789125684</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.190891412082053</c:v>
+                  <c:v>2.787785211871676</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.21694872915756</c:v>
+                  <c:v>3.015247447990697</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.066748999360186</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.630592820205351</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2.490290789125684</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.787785211871676</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.015247447990697</c:v>
-                </c:pt>
-                <c:pt idx="12">
                   <c:v>2.771950131423473</c:v>
                 </c:pt>
               </c:numCache>
@@ -664,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -680,105 +650,65 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="B2" s="1">
-        <v>1.210450846384477</v>
+        <v>2.1940279781695</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="B3" s="1">
-        <v>1.821409419552876</v>
+        <v>2.248173359145694</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="B4" s="1">
-        <v>2.394848414965141</v>
+        <v>2.081628401803384</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="B5" s="1">
-        <v>2.148061589221886</v>
+        <v>2.630592820205351</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B6" s="1">
-        <v>2.084784555677182</v>
+        <v>2.490290789125684</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="B7" s="1">
-        <v>2.190891412082053</v>
+        <v>2.787785211871676</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B8" s="1">
-        <v>2.21694872915756</v>
+        <v>3.015247447990697</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="B9" s="1">
-        <v>2.066748999360186</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B10" s="1">
-        <v>2.630592820205351</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B11" s="1">
-        <v>2.490290789125684</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2.787785211871676</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B13" s="1">
-        <v>3.015247447990697</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B14" s="1">
         <v>2.771950131423473</v>
       </c>
     </row>

--- a/output_data/charts/0500000US39127.xlsx
+++ b/output_data/charts/0500000US39127.xlsx
@@ -161,32 +161,41 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$9</c:f>
+              <c:f>Sheet1!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -194,32 +203,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$9</c:f>
+              <c:f>Sheet1!$B$2:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
+                  <c:v>2.545635167018502</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.148061589221886</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.054930838889442</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2.1940279781695</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>2.248173359145694</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>2.081628401803384</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>2.630592820205351</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>2.490290789125684</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>2.787785211871676</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>3.015247447990697</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>2.771950131423473</c:v>
                 </c:pt>
               </c:numCache>
@@ -634,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -650,65 +668,89 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B2" s="1">
-        <v>2.1940279781695</v>
+        <v>2.545635167018502</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B3" s="1">
-        <v>2.248173359145694</v>
+        <v>2.148061589221886</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B4" s="1">
-        <v>2.081628401803384</v>
+        <v>2.054930838889442</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B5" s="1">
-        <v>2.630592820205351</v>
+        <v>2.1940279781695</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B6" s="1">
-        <v>2.490290789125684</v>
+        <v>2.248173359145694</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B7" s="1">
-        <v>2.787785211871676</v>
+        <v>2.081628401803384</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B8" s="1">
-        <v>3.015247447990697</v>
+        <v>2.630592820205351</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2.490290789125684</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2.787785211871676</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3.015247447990697</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
         <v>2024</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B12" s="1">
         <v>2.771950131423473</v>
       </c>
     </row>
